--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2020_metropolitana.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_basneta_a_2020_metropolitana.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:16</t>
+    <t xml:space="preserve">2026-09-24 01:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -684,10 +684,10 @@
         <v>0.26</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9">
@@ -704,13 +704,13 @@
         <v>52</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="10">
@@ -730,7 +730,7 @@
         <v>0.22</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.03</v>
@@ -744,7 +744,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>52</v>
@@ -753,7 +753,7 @@
         <v>0.11</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.21</v>
@@ -796,13 +796,13 @@
         <v>52</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -819,13 +819,13 @@
         <v>52</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.29</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="15">
@@ -845,7 +845,7 @@
         <v>0.2</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.02</v>
